--- a/leads/sabusinessdirectories_contacts (4).xlsx
+++ b/leads/sabusinessdirectories_contacts (4).xlsx
@@ -5,21 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\leads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17970" windowHeight="6030"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17970" windowHeight="6030"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>Name</t>
   </si>
@@ -27,36 +27,15 @@
     <t>Telephone</t>
   </si>
   <si>
-    <t>Pretoria</t>
-  </si>
-  <si>
     <t>Not available</t>
   </si>
   <si>
     <t>ORION HOTEL (Katse LodgeKatse Dam, LESOTHO)</t>
   </si>
   <si>
-    <t>Hotel +266 2891 0202 Toll free 086 199 1199 Central Reservations +27 (0)11 403 1218</t>
-  </si>
-  <si>
     <t>ORION HOTEL (Mohale LodgeMohale Dam, LESOTHO)</t>
   </si>
   <si>
-    <t>Hotel +266 2293 6432 Toll free 086 199 1199 Central Reservations +27 (0)11 403 1218</t>
-  </si>
-  <si>
-    <t>4PL. COM (PTY) LTD</t>
-  </si>
-  <si>
-    <t>Number: 012 345 5046</t>
-  </si>
-  <si>
-    <t>DE JAGER &amp; DU PLESSIS ATTORNEYS</t>
-  </si>
-  <si>
-    <t>LENBERG,363 PRETORIA AVENUE,FENDALE,RANDBURG,2194</t>
-  </si>
-  <si>
     <t>AVBOB (BRITS)</t>
   </si>
   <si>
@@ -333,19 +312,25 @@
     <t>DE MERINDOL ANTIQUES &amp; ART</t>
   </si>
   <si>
-    <t>012-362 0654 CELL: 082 460 1728 / 084 602 5808 EMAIL: marc@demerindol.co.za TRADE HEADING ANTIQUE DEALERS</t>
-  </si>
-  <si>
     <t>TEAZERS PRETORIA</t>
   </si>
   <si>
-    <t>012-332 7108 CELL: 072 139 7108 FAX: 012-332 4852 EMAIL: pretoria@teazers.co.za TRADE HEADING ADULT ENTERTAINMENT</t>
-  </si>
-  <si>
     <t>MAGIC ASSEMBLIES</t>
   </si>
   <si>
     <t>TON</t>
+  </si>
+  <si>
+    <t>Hotel +266 2891 0202 Central Reservations +27 (0)11 403 1218</t>
+  </si>
+  <si>
+    <t>Hotel +266 2293 6432 Central Reservations +27 (0)11 403 1218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">012-332 7108 CELL: 072 139 7108 </t>
+  </si>
+  <si>
+    <t>012-362 0654 CELL: 082 460 1728 / 084 602 5808</t>
   </si>
 </sst>
 </file>
@@ -708,8 +693,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -721,10 +710,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -732,423 +721,399 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
         <v>63</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
         <v>65</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
         <v>67</v>
-      </c>
-      <c r="B35" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
         <v>71</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
         <v>73</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
         <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
         <v>77</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
         <v>79</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
         <v>81</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
         <v>85</v>
-      </c>
-      <c r="B44" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
         <v>87</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
         <v>89</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
         <v>91</v>
-      </c>
-      <c r="B47" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
         <v>95</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
